--- a/app/doc/개발/70_테스트후_수정리스트.xlsx
+++ b/app/doc/개발/70_테스트후_수정리스트.xlsx
@@ -672,17 +672,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>매핑 테이블 물류코드 실데이터 확인</t>
+          <t>ERP 데이터 입력 (롯데 업체코드값 업무 담당 확인)</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>search_shipment_lotte.jsp 의 COALESCE(M1.물류코드, M2.물류코드) 값을 그대로 사용 (원인 추정, 실데이터 미확인)</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
+          <t>[2026-10-06 운영DB 확인] 롯데 출고 7건 모두 M1(점포 거래처) 매핑 없음, M2(상위 A00565) 매핑 1건(SEQ 42, 품목 1110100681, 타입구분 W, 바코드타입 L0)의 물류코드 빈 값 → EMARTLOGIS_CODE 빈 값 → 라벨 회사코드·바코드 앞자리 누락. 원본은 B_COMMON_CODE LOTTE_STORE_CODE(센터코드 기준) REF_CODE2, 없으면 '회사코드없음'</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>코드 수정 없음. 조치안: ERP CO_매출처품목코드매핑 A00565/1110100681(SEQ 42) 물류코드에 롯데 업체코드 입력. (선택) JSP 빈 값 시 원본처럼 '회사코드없음' 기본값</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K6" s="6" t="inlineStr"/>
     </row>
     <row r="7" ht="48" customHeight="1">
@@ -713,17 +725,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>바코드 정보의 제조일 위치(FROM~TO) 설정 확인</t>
+          <t>ERP 데이터 수정 (CO_품목코드 제조일자시작 6 → 8)</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>스캔 바코드를 MAKINGDATE_FROM~TO 로 잘라낸 값을 그대로 사용. 로직 구조는 원본과 동일 (원인 추정)</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="5" t="inlineStr"/>
+          <t>[2026-10-06 운영DB 확인] CO_품목코드 1110100681 제조일자시작 6, 끝 13. 계근 바코드(예: 00603 20260928 1110100681)의 6~13 = YYYYMMDD 8자리 절사 → SM_출고계근.제조일자 스캔 10건 20260928 저장. 라벨은 6자리(YYMMDD) 가정 → 제조일자 '2020년 26월 09일' 오출력, 롯데 바코드 2자리 증가. 수기 입력 건은 6자리 정상. 앱 절사 로직은 원본 동일. 품목은 마트사 간 비공유 → 롯데만 영향</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>코드 수정 없음. 조치안: ERP CO_품목코드 1110100681 제조일자시작 6 → 8 (8~13 = YYMMDD 6자리)</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="48" customHeight="1">
@@ -831,12 +855,12 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>대기</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>원본에 없는 기능 — 추가 여부 결정</t>
+          <t>사용자 결정: 메인 화면만, yyyy-MM-dd 형식 (원본에 없는 기능, 승인 예외)</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -844,9 +868,21 @@
           <t>원본에 없는 기능</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>MainActivity 액션바 subtitle에 '작업일자 : yyyy-MM-dd' 표시. showWorkDate() 추가, onResume·날짜 선택·TEST_MODE·출하대상받기 4곳 호출. Common.selectDay·조회 로직 변경 없음. EDA51 실기기 시나리오 1~4 PASS, 통합 테스트 대기</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>MainActivity.java</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>개발/72</t>
+        </is>
+      </c>
       <c r="K10" s="6" t="inlineStr"/>
     </row>
     <row r="11" ht="48" customHeight="1">
@@ -1205,7 +1241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1434,6 +1470,108 @@
       <c r="H8" s="5" t="inlineStr">
         <is>
           <t>커밋</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>46301</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>운영DB 조회로 원인 확정: A00565 매핑 물류코드 빈 값. 조치안 ERP 물류코드 입력</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n"/>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>원인 확정, ERP 조치 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>46301</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>운영DB 조회로 원인 확정: 1110100681 제조일자시작 6(8자리 절사). 조치안 6 → 8</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>원인 확정, ERP 조치 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>46301</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>메인 화면 작업일자 표시 추가 및 EDA51 실기기 확인(미선택 오늘·즉시 반영·재진입 유지·출하대상받기 조회조건 불변 PASS)</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>MainActivity.java</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>개발/72</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>통합 테스트 대기</t>
         </is>
       </c>
     </row>

--- a/app/doc/개발/70_테스트후_수정리스트.xlsx
+++ b/app/doc/개발/70_테스트후_수정리스트.xlsx
@@ -949,22 +949,34 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>대기</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>미사용 타입 분기 삭제 / 사용 차단 중 결정. E2 결과 반영 권장</t>
+          <t>사용자 결정 2026-10-06: M0·M8·M9·H2·H5·L0 외 타입 분기 제거</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>LabelPrintHelper 에 M1·M3·M4·E0~E3·P0 분기 잔존. H2·H5 위치 미확인</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
+          <t>[2026-10-06] ERP 매핑 등록 타입: M0·M9·H2·H5·L0(W/B), E2·C1(J, PDA 미유입). 앱 잔존 분기 M1·M3·M4·E0~E3·P0 (LabelPrintHelper 단일 파일). H2·H5는 홈플러스 라벨이 타입 분기 없음</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>LabelPrintHelper 미사용 타입 case·if 분기·상수·Javadoc 제거(참조 0건). 코드검증·원본비교 PASS. EDA51 변경 전후 재출력 바이트 일치(M0 13908, M9 11762). L0·홈플러스 실출력은 데이터 없음, 출력물 육안 확인 대기</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>LabelPrintHelper.java</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>개발/73</t>
+        </is>
+      </c>
       <c r="K12" s="6" t="inlineStr"/>
     </row>
     <row r="13" ht="48" customHeight="1">
@@ -1241,7 +1253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1572,6 +1584,44 @@
       <c r="H11" s="5" t="inlineStr">
         <is>
           <t>통합 테스트 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>46301</v>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>미사용 바코드 타입(M1·M3·M4·E0~E3·P0) 분기 제거, 변경 전후 M0·M9 라벨 전송 바이트 일치 확인</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>LabelPrintHelper.java</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>62053c0</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>개발/73</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>육안 확인·통합 테스트 대기</t>
         </is>
       </c>
     </row>

--- a/app/doc/개발/70_테스트후_수정리스트.xlsx
+++ b/app/doc/개발/70_테스트후_수정리스트.xlsx
@@ -964,7 +964,7 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>LabelPrintHelper 미사용 타입 case·if 분기·상수·Javadoc 제거(참조 0건). 코드검증·원본비교 PASS. EDA51 변경 전후 재출력 바이트 일치(M0 13908, M9 11762). L0·홈플러스 실출력은 데이터 없음, 출력물 육안 확인 대기</t>
+          <t>LabelPrintHelper 미사용 타입 case·if 분기·상수·Javadoc 제거(참조 0건, 구버전 ShipmentActivity 제외). 코드검증·원본비교 PASS. EDA51 변경 전후 재출력 바이트 일치(M0 13908, M9 11762). 통합테스트: M0·M9·L0·H2·H5 실출력 전송 확인. M8·미트센터9231·킬코이 데이터 없음 미수행. 출력물 육안 확인 대기</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1253,7 +1253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1622,6 +1622,40 @@
       <c r="H12" s="5" t="inlineStr">
         <is>
           <t>육안 확인·통합 테스트 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>46301</v>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>개발 73 Step 5 통합 테스트: L0(롯데 09-29)·H2(홈플러스 09-30)·H5(홈플러스 비정량 09-28) 신규 계근 출력 확인. M8·미트센터·킬코이는 운영 데이터 없음</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>개발/73</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>육안 확인 대기</t>
         </is>
       </c>
     </row>

--- a/app/doc/개발/70_테스트후_수정리스트.xlsx
+++ b/app/doc/개발/70_테스트후_수정리스트.xlsx
@@ -949,7 +949,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>LabelPrintHelper 미사용 타입 case·if 분기·상수·Javadoc 제거(참조 0건, 구버전 ShipmentActivity 제외). 코드검증·원본비교 PASS. EDA51 변경 전후 재출력 바이트 일치(M0 13908, M9 11762). 통합테스트: M0·M9·L0·H2·H5 실출력 전송 확인. M8·미트센터9231·킬코이 데이터 없음 미수행. 출력물 육안 확인 대기</t>
+          <t>LabelPrintHelper 미사용 타입 case·if 분기·상수·Javadoc 제거(참조 0건, 구버전 ShipmentActivity 제외). 코드검증·원본비교 PASS. EDA51 변경 전후 재출력 바이트 일치(M0 13908, M9 11762). 통합테스트: M0·M9·L0·H2·H5 실출력 전송 확인. M8·미트센터9231·킬코이 데이터 없음 미수행. 출력물 육안 정상 확인</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -977,7 +977,9 @@
           <t>개발/73</t>
         </is>
       </c>
-      <c r="K12" s="6" t="inlineStr"/>
+      <c r="K12" s="6" t="n">
+        <v>46301</v>
+      </c>
     </row>
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -1253,7 +1255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1656,6 +1658,40 @@
       <c r="H13" s="5" t="inlineStr">
         <is>
           <t>육안 확인 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>46301</v>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>출력 라벨 육안 정상 확인(사용자) → 완료 처리</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>개발/73</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
     </row>

--- a/app/doc/개발/70_테스트후_수정리스트.xlsx
+++ b/app/doc/개발/70_테스트후_수정리스트.xlsx
@@ -855,7 +855,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>MainActivity 액션바 subtitle에 '작업일자 : yyyy-MM-dd' 표시. showWorkDate() 추가, onResume·날짜 선택·TEST_MODE·출하대상받기 4곳 호출. Common.selectDay·조회 로직 변경 없음. EDA51 실기기 시나리오 1~4 PASS, 통합 테스트 대기</t>
+          <t>MainActivity 액션바 subtitle에 '작업일자 : yyyy-MM-dd' 표시. showWorkDate() 추가, onResume·날짜 선택·TEST_MODE·출하대상받기 4곳 호출. Common.selectDay·조회 로직 변경 없음. EDA51 실기기 시나리오 1~4 PASS, 통합 테스트 5항목 PASS(변경 전후 이마트 09-28 조회 5/2/6건 동일)</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -883,7 +883,9 @@
           <t>개발/72</t>
         </is>
       </c>
-      <c r="K10" s="6" t="inlineStr"/>
+      <c r="K10" s="6" t="n">
+        <v>46301</v>
+      </c>
     </row>
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -1255,7 +1257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1690,6 +1692,40 @@
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>46301</v>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>개발 72 Step 3 통합 테스트 5항목 PASS, 변경 전 빌드와 출하대상 조회 결과 동일 확인 → 완료</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>개발/72</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>완료</t>
         </is>

--- a/app/doc/개발/70_테스트후_수정리스트.xlsx
+++ b/app/doc/개발/70_테스트후_수정리스트.xlsx
@@ -720,7 +720,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>대기</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -735,20 +735,22 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>코드 수정 없음. 조치안: ERP CO_품목코드 1110100681 제조일자시작 6 → 8 (8~13 = YYMMDD 6자리)</t>
+          <t>코드 수정 없음. DB(weberp_hl) CO_품목코드 1110100681 제조일자시작 6 → 8 UPDATE(사용자 실행). EDA51 롯데 09-29 재계근: 절사 제조일 260929(6자리), 라벨 2026년 09월 29일, 바코드 26092906338809790013 정상 — 출력물 육안 확인 완료</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
+          <t>-(DB 데이터)</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="K7" s="6" t="n">
+        <v>46301</v>
+      </c>
     </row>
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -1257,7 +1259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1726,6 +1728,40 @@
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>46301</v>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>CO_품목코드 1110100681 제조일자시작 6→8 UPDATE 후 롯데 라벨 제조일 6자리 정상 출력 확인 → 완료</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>오류/(미작성)</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>완료</t>
         </is>

--- a/app/doc/개발/70_테스트후_수정리스트.xlsx
+++ b/app/doc/개발/70_테스트후_수정리스트.xlsx
@@ -692,7 +692,7 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>오류/39</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr"/>
@@ -745,7 +745,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>오류/40</t>
         </is>
       </c>
       <c r="K7" s="6" t="n">
@@ -1279,6 +1279,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -1758,7 +1759,7 @@
       <c r="F16" s="4" t="n"/>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>오류/(미작성)</t>
+          <t>오류/40</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">

--- a/app/doc/개발/70_테스트후_수정리스트.xlsx
+++ b/app/doc/개발/70_테스트후_수정리스트.xlsx
@@ -780,17 +780,21 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>화면 표시 문제와 실제 데이터 누락·중복을 구분</t>
+          <t>원본 동일 결함 — 수정 여부 결정 (안1 일괄전송 조기 return 제거 / 안2 SEND_Y 집계 수정)</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>미조사</t>
+          <t>[2026-10-07 원인 확정] SM_출고계근 출고상세 508(이마트 비정량) 순번 2·3이 18초 뒤 재INSERT(SEQ 258·259). 원인: count(SAVE_TYPE='Y') 전체행 집계로 SAVE_CNT 부풀림 + 일괄전송 후 Y 처리 루프 조기 return → F 잔류(B1) → 재전송 중복(B2). B1·B2 동일 원인, 원본 동일</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>오류/41</t>
+        </is>
+      </c>
       <c r="K8" s="6" t="inlineStr"/>
     </row>
     <row r="9" ht="48" customHeight="1">
@@ -821,17 +825,21 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>ERP 수신 건수·중량·이력번호 대사</t>
+          <t>원본 동일 결함 — 수정 여부 결정 (안1 일괄전송 조기 return 제거 / 안2 SEND_Y 집계 수정)</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>미조사</t>
+          <t>[2026-10-07 원인 확정] SM_출고계근 출고상세 508(이마트 비정량) 순번 2·3이 18초 뒤 재INSERT(SEQ 258·259). 원인: count(SAVE_TYPE='Y') 전체행 집계로 SAVE_CNT 부풀림 + 일괄전송 후 Y 처리 루프 조기 return → F 잔류(B1) → 재전송 중복(B2). B1·B2 동일 원인, 원본 동일</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>오류/41</t>
+        </is>
+      </c>
       <c r="K9" s="6" t="inlineStr"/>
     </row>
     <row r="10" ht="48" customHeight="1">
@@ -1259,7 +1267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1279,7 +1287,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -1765,6 +1772,40 @@
       <c r="H16" s="5" t="inlineStr">
         <is>
           <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>B1/B2</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>운영DB·코드 조사로 원인 확정(일괄전송 조기 종료 + SEND_Y 집계 오류), 오류 41 문서화. 원본 동일 결함</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>오류/41</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>수정 여부 결정 대기</t>
         </is>
       </c>
     </row>

--- a/app/doc/개발/70_테스트후_수정리스트.xlsx
+++ b/app/doc/개발/70_테스트후_수정리스트.xlsx
@@ -20,9 +20,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -775,7 +776,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>대기</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -788,14 +789,24 @@
           <t>[2026-10-07 원인 확정] SM_출고계근 출고상세 508(이마트 비정량) 순번 2·3이 18초 뒤 재INSERT(SEQ 258·259). 원인: count(SAVE_TYPE='Y') 전체행 집계로 SAVE_CNT 부풀림 + 일괄전송 후 Y 처리 루프 조기 return → F 잔류(B1) → 재전송 중복(B2). B1·B2 동일 원인, 원본 동일</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>안1 적용: 일괄전송 Y 처리 루프의 조기 return 제거, 루프 종료 후 jChk&gt;0 &amp;&amp; jChk==arSM.size() 이면 'ss' 판정. count(SAVE_TYPE='Y') 집계(안2)는 원본 동일로 유지. [2026-10-12 EDA51] 서버 계근 삭제 후 이마트 비정량 508: 미전송 2건+신규 1건 일괄전송 → 서버 3건(계근순번 3·6·7 중복 없음), 로컬 3건 전부 Y. 홈플러스 비정량 499: 미전송 3건 일괄전송 → 서버 3건, 로컬 전부 Y, 재전송 시 'af'(이미 전송) 중복 0건. 도매 일괄 5건도 동일 경로 정상</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>BixolonShipmentActivity.java (ProgressDlgShipmentSend 일괄전송)</t>
+        </is>
+      </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>오류/41</t>
-        </is>
-      </c>
-      <c r="K8" s="6" t="inlineStr"/>
+          <t>오류/41, 개발/74</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>46307</v>
+      </c>
     </row>
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -820,7 +831,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>대기</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -833,14 +844,24 @@
           <t>[2026-10-07 원인 확정] SM_출고계근 출고상세 508(이마트 비정량) 순번 2·3이 18초 뒤 재INSERT(SEQ 258·259). 원인: count(SAVE_TYPE='Y') 전체행 집계로 SAVE_CNT 부풀림 + 일괄전송 후 Y 처리 루프 조기 return → F 잔류(B1) → 재전송 중복(B2). B1·B2 동일 원인, 원본 동일</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>안1 적용: 일괄전송 Y 처리 루프의 조기 return 제거, 루프 종료 후 jChk&gt;0 &amp;&amp; jChk==arSM.size() 이면 'ss' 판정. count(SAVE_TYPE='Y') 집계(안2)는 원본 동일로 유지. [2026-10-12 EDA51] 서버 계근 삭제 후 이마트 비정량 508: 미전송 2건+신규 1건 일괄전송 → 서버 3건(계근순번 3·6·7 중복 없음), 로컬 3건 전부 Y. 홈플러스 비정량 499: 미전송 3건 일괄전송 → 서버 3건, 로컬 전부 Y, 재전송 시 'af'(이미 전송) 중복 0건. 도매 일괄 5건도 동일 경로 정상</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>BixolonShipmentActivity.java (ProgressDlgShipmentSend 일괄전송)</t>
+        </is>
+      </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>오류/41</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="inlineStr"/>
+          <t>오류/41, 개발/74</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>46307</v>
+      </c>
     </row>
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -1267,7 +1288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1806,6 +1827,82 @@
       <c r="H17" s="5" t="inlineStr">
         <is>
           <t>수정 여부 결정 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>일괄전송 Y 처리 루프 조기 return 제거(안1) → 루프 종료 후 'ss' 판정. EDA51 이마트 비정량 508·홈플러스 비정량 499 일괄전송 실기기 확인</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>BixolonShipmentActivity.java</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>732b65a</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>오류/41, 개발/74</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>일괄전송 후 로컬 F 잔류 해소</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>일괄전송 Y 처리 루프 조기 return 제거(안1) → 루프 종료 후 'ss' 판정. EDA51 이마트 비정량 508·홈플러스 비정량 499 일괄전송 실기기 확인</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>BixolonShipmentActivity.java</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>732b65a</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>오류/41, 개발/74</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>재전송 중복 0건 확인</t>
         </is>
       </c>
     </row>
@@ -1838,6 +1935,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -2059,6 +2157,7 @@
         <v/>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>

--- a/app/doc/개발/70_테스트후_수정리스트.xlsx
+++ b/app/doc/개발/70_테스트후_수정리스트.xlsx
@@ -537,6 +537,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -941,22 +942,32 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>대기</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>파렛트 구분 방법 결정</t>
+          <t>36건(6열×6행) 고정 단위라 파렛트별 총 중량 구분 불가. 파렛트 구분 방법: 파렛트당 박스 수 지정(사용자 결정)</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>현재는 36건(6열×6행) 단위로 'N번 총 중량'만 출력. 파렛트 구분 기준 없음</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
+          <t>합산 버튼 → 파렛트당 박스 수 입력 창(기본 36, 0·공백 안내). 박스 수 단위로 'N번 총 중량' 출력, 파렛트가 36건 초과 시 36건마다 총 중량 없는 라벨 이어서 출력. 36 입력 시 수정 전과 바이트 동일(5189). 실기기 출력 전송 완료, 출력물 육안 확인 대기</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>BixolonShipmentActivity.java (detail_btn_sum, printSumLabel)</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>개발/79</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>46307</v>
+      </c>
       <c r="K11" s="6" t="inlineStr"/>
     </row>
     <row r="12" ht="48" customHeight="1">
@@ -1288,7 +1299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1903,6 +1914,44 @@
       <c r="H19" s="5" t="inlineStr">
         <is>
           <t>재전송 중복 0건 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>합산 라벨 파렛트당 박스 수 지정. EDA51: 36=수정 전 5189 bytes 동일, 2→2장, 40(43건)→3장, 0·취소 인쇄 없음. 임시 계근 40건은 테스트 후 원복</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>BixolonShipmentActivity.java</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>개발 79 Step 1~2</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>개발/79</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>출력물 육안 확인 대기</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1984,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -2157,7 +2205,6 @@
         <v/>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>

--- a/app/doc/개발/70_테스트후_수정리스트.xlsx
+++ b/app/doc/개발/70_테스트후_수정리스트.xlsx
@@ -537,7 +537,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1299,7 +1298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1950,6 +1949,44 @@
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>출력물 육안 확인 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>합산 라벨 총 중량 5자리 이상 잘림 수정: 폭 측정 후 넘칠 때만 x 왼쪽 이동(최소 10)·글자 크기 축소(최소 40). EDA51: 52.9 x=100 그대로(5189 bytes 동일), 9961.2 x=60, 12062.9 x=26. 임시 계근은 원복</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>BixolonShipmentActivity.java, LabelPrintHelper.java</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>개발 79 Step 3</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>개발/79</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>출력물 육안 확인 대기</t>
         </is>

--- a/app/doc/개발/70_테스트후_수정리스트.xlsx
+++ b/app/doc/개발/70_테스트후_수정리스트.xlsx
@@ -1298,7 +1298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1989,6 +1989,44 @@
       <c r="H21" s="5" t="inlineStr">
         <is>
           <t>출력물 육안 확인 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>SM_출고계근 라벨 출력 정보 11컬럼 INSERT: 앱 최초 출력값 기록→TB_GOODS_WET→패킷[15]~[25], JSP 4종 INSERT. EDA51: 이마트 SEQ 285~289, 롯데 290~295, 도매(일괄) 296~300 적재 확인, 라벨 바이트 동일</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>LabelPrintHelper·라벨클래스·DBHandler·BixolonShipmentActivity 외, insert_goods_wet*.jsp 4종</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>개발 80 Step 1~3</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>개발/80</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>출력값 있는 일괄 전송 미수행</t>
         </is>
       </c>
     </row>

--- a/app/doc/개발/70_테스트후_수정리스트.xlsx
+++ b/app/doc/개발/70_테스트후_수정리스트.xlsx
@@ -1211,7 +1211,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>보류</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1221,12 +1221,20 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>최신 소스 미수령</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr"/>
+          <t>[2026-10-22] 최신 소스 수령: D:\PDA\PDA-INNO_20261021\PDA-INNO\PDA-INNO (2026-10-21 스냅샷, git). 구 원본 대비 다른 파일 4개(ShipmentActivity·LoginActivity·Common·ProgressDlgShipSearch)+strings.xml. 현재 소스 대비 누락·불일치 5건: ① 롯데 라벨 출력 이력 적재(앱·JSP·테이블 없음) ② 합산 파렛트 출력 문구·입력 창 ③ 이마트 비정량 스캔 매칭(앞 6자리) ④ M9 대구센터만 점포명·점포코드 출력 ⑤ TRD 소비기한 체크 조건(contains TRD). 영향 없음: EMART_PLANT_CODE 길이 체크·M1 else if·로그·로고</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>② 합산 파렛트 출력부터 처리 — 오류/44 문서화, 개발/86 작성 (코드 수정 대기)</t>
+        </is>
+      </c>
       <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>오류/44, 개발/86</t>
+        </is>
+      </c>
       <c r="K17" s="6" t="inlineStr"/>
     </row>
     <row r="18" ht="48" customHeight="1">
@@ -1298,7 +1306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2027,6 +2035,40 @@
       <c r="H22" s="5" t="inlineStr">
         <is>
           <t>출력값 있는 일괄 전송 미수행</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>최신 소스(PDA-INNO_20261021) 비교: 누락·불일치 5건 확인. 합산 파렛트 출력 최신 원본 불일치 오류 44 문서화, 개발 86(입력 창·라벨 최신 원본 동일화, 총 중량 넘칠 때만 크기 축소 — 사용자 결정) 작성</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>오류/44, 개발/86</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>코드 수정 대기</t>
         </is>
       </c>
     </row>

--- a/app/doc/개발/70_테스트후_수정리스트.xlsx
+++ b/app/doc/개발/70_테스트후_수정리스트.xlsx
@@ -941,7 +941,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -964,8 +964,10 @@
           <t>개발/79</t>
         </is>
       </c>
-      <c r="J11" s="5" t="n">
-        <v>46307</v>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>개발/79, 오류/44, 개발/86</t>
+        </is>
       </c>
       <c r="K11" s="6" t="inlineStr"/>
     </row>
@@ -1306,7 +1308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2069,6 +2071,44 @@
       <c r="H23" s="5" t="inlineStr">
         <is>
           <t>코드 수정 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>최신 원본 동일화(개발 86 Step 1): 박스 수 입력 창을 palletCountDialog()로 분리, 제목 "파렛트당 박스 수"·메시지·토스트 "정확히 입력하세요"·setCancelable(false)·잘못 입력 시 재표시를 최신 원본과 같게. 컴파일·코드검증·원본비교 PASS</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>WetDetailDialog.java</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>개발 86 Step 1</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>오류/44, 개발/86</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>EDA51 미연결 — 실기기 확인은 Step 3</t>
         </is>
       </c>
     </row>

--- a/app/doc/개발/70_테스트후_수정리스트.xlsx
+++ b/app/doc/개발/70_테스트후_수정리스트.xlsx
@@ -1308,7 +1308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2107,6 +2107,44 @@
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>EDA51 미연결 — 실기기 확인은 Step 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>최신 원본 동일화(개발 86 Step 2): SumLabel 인쇄 루프를 최신 원본 printSumLabel 구조로 교체 — 장마다 (현재장/장 수), 파렛트 마지막 장 "N박스 총 중량 :" (95,380) 37 + 중량 (360,355) 75. 개별 중량 32/95 유지, 총 중량은 폭 576 초과 시만 크기 축소(1234.5→69). 기존 "N번 총 중량"·x 왼쪽 이동 제거. 컴파일·코드검증·원본비교 PASS</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>SumLabel.java</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>개발 86 Step 2</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>오류/44, 개발/86</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>EDA51 미연결 — 실기기 확인은 Step 3</t>
         </is>
